--- a/hexaly_benchmarking_results/mip_n.xlsx
+++ b/hexaly_benchmarking_results/mip_n.xlsx
@@ -19,22 +19,22 @@
     <t>acc</t>
   </si>
   <si>
-    <t>T1_U1</t>
+    <t>T3_U2</t>
   </si>
   <si>
-    <t>T2_U2</t>
+    <t>T2_U3</t>
   </si>
   <si>
     <t>T4_U2</t>
   </si>
   <si>
+    <t>T1_U1</t>
+  </si>
+  <si>
     <t>T3_U3</t>
   </si>
   <si>
-    <t>T3_U2</t>
-  </si>
-  <si>
-    <t>T2_U3</t>
+    <t>T2_U2</t>
   </si>
   <si>
     <t>T4_U3</t>
@@ -467,7 +467,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -479,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -493,7 +493,7 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -502,7 +502,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -522,7 +522,7 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -560,10 +560,10 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -580,10 +580,10 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -592,10 +592,10 @@
         <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -609,10 +609,10 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -621,10 +621,10 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -638,7 +638,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -647,10 +647,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -667,22 +667,22 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -696,22 +696,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -725,7 +725,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -734,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -754,7 +754,7 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -766,7 +766,7 @@
         <v>3</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -783,22 +783,22 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
         <v>5</v>
       </c>
-      <c r="F14">
-        <v>7</v>
-      </c>
       <c r="G14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -812,22 +812,22 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
         <v>7</v>
       </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
       <c r="G15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -841,22 +841,22 @@
         <v>6</v>
       </c>
       <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
         <v>5</v>
       </c>
-      <c r="C16">
+      <c r="F16">
+        <v>7</v>
+      </c>
+      <c r="G16">
         <v>6</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16">
-        <v>7</v>
-      </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>4</v>
       </c>
       <c r="H16">
         <v>8</v>
@@ -870,28 +870,28 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H17">
+        <v>8</v>
+      </c>
+      <c r="I17">
         <v>6</v>
-      </c>
-      <c r="I17">
-        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -899,22 +899,22 @@
         <v>4</v>
       </c>
       <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>16</v>
+      </c>
+      <c r="E18">
         <v>6</v>
       </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>17</v>
-      </c>
-      <c r="E18">
-        <v>12</v>
-      </c>
       <c r="F18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>4</v>
@@ -928,25 +928,25 @@
         <v>3</v>
       </c>
       <c r="B19">
+        <v>11</v>
+      </c>
+      <c r="C19">
         <v>8</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
       </c>
       <c r="D19">
         <v>19</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -957,25 +957,25 @@
         <v>2</v>
       </c>
       <c r="B20">
+        <v>26</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20">
         <v>10</v>
       </c>
-      <c r="C20">
-        <v>8</v>
-      </c>
-      <c r="D20">
-        <v>26</v>
-      </c>
-      <c r="E20">
+      <c r="F20">
         <v>13</v>
       </c>
-      <c r="F20">
-        <v>26</v>
-      </c>
       <c r="G20">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -986,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>55</v>
@@ -998,10 +998,10 @@
         <v>15</v>
       </c>
       <c r="F21">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H21">
         <v>3</v>

--- a/hexaly_benchmarking_results/mip_n.xlsx
+++ b/hexaly_benchmarking_results/mip_n.xlsx
@@ -19,16 +19,13 @@
     <t>acc</t>
   </si>
   <si>
-    <t>T3_U2</t>
-  </si>
-  <si>
-    <t>T2_U3</t>
-  </si>
-  <si>
     <t>T4_U2</t>
   </si>
   <si>
-    <t>T1_U1</t>
+    <t>T4_U3</t>
+  </si>
+  <si>
+    <t>T3_U2</t>
   </si>
   <si>
     <t>T3_U3</t>
@@ -37,7 +34,10 @@
     <t>T2_U2</t>
   </si>
   <si>
-    <t>T4_U3</t>
+    <t>T1_U1</t>
+  </si>
+  <si>
+    <t>T2_U3</t>
   </si>
   <si>
     <t>T5_U4</t>
@@ -464,25 +464,25 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -493,25 +493,25 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -522,19 +522,19 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -551,19 +551,19 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -580,13 +580,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -598,7 +598,7 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -609,22 +609,22 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -638,25 +638,25 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -667,25 +667,25 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -696,22 +696,22 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -725,25 +725,25 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12">
         <v>3</v>
@@ -754,14 +754,14 @@
         <v>9</v>
       </c>
       <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
         <v>9</v>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
       <c r="E13">
         <v>3</v>
       </c>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -783,25 +783,25 @@
         <v>8</v>
       </c>
       <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
         <v>7</v>
       </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -812,25 +812,25 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -841,25 +841,25 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -870,22 +870,22 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>8</v>
@@ -899,25 +899,25 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E18">
+        <v>13</v>
+      </c>
+      <c r="F18">
         <v>6</v>
       </c>
-      <c r="F18">
-        <v>11</v>
-      </c>
       <c r="G18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -928,25 +928,25 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I19">
         <v>8</v>
@@ -960,25 +960,25 @@
         <v>26</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E20">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20">
         <v>10</v>
       </c>
-      <c r="F20">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
       <c r="H20">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -986,28 +986,28 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>50</v>
+      </c>
+      <c r="E21">
+        <v>16</v>
+      </c>
+      <c r="F21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>55</v>
-      </c>
-      <c r="E21">
+      <c r="G21">
+        <v>16</v>
+      </c>
+      <c r="H21">
+        <v>16</v>
+      </c>
+      <c r="I21">
         <v>15</v>
-      </c>
-      <c r="F21">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>14</v>
-      </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
